--- a/artfynd/A 1414-2024 artfynd.xlsx
+++ b/artfynd/A 1414-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1414-2024 artfynd.xlsx
+++ b/artfynd/A 1414-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113702962</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,12 +779,7 @@
         <v>113703033</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113702735</v>
+        <v>113703039</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
+          <t>Medbön, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317449</v>
+        <v>317452</v>
       </c>
       <c r="R4" t="n">
-        <v>6514328</v>
+        <v>6514375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,50 +978,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703039</v>
+        <v>113702683</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Medbön, Dls</t>
+          <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317452</v>
+        <v>317387</v>
       </c>
       <c r="R5" t="n">
-        <v>6514375</v>
+        <v>6514293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,55 +1084,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113702683</v>
+        <v>113702735</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Petersborg, Lerdal, Västra Götaland, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317387</v>
+        <v>317449</v>
       </c>
       <c r="R6" t="n">
-        <v>6514293</v>
+        <v>6514328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 1414-2024 artfynd.xlsx
+++ b/artfynd/A 1414-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702962</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703033</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702683</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113702735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>